--- a/resultados_gpt_oss/eval_comparison.xlsx
+++ b/resultados_gpt_oss/eval_comparison.xlsx
@@ -115,13 +115,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -177,6 +180,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -544,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:S101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -552,10 +558,20 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="70" customWidth="1" min="17" max="17"/>
+    <col width="70" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -586,22 +602,72 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>llm_nome_nivel</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ponto_decisao</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>recursos_estimados</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>recursos_detalhados</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>sinais_vitais_zona_perigo</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>populacao_especial</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>over_triage_aplicado</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>llm_confianca</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>match</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>validation_errors</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>validation_warnings</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>justificativa</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>alertas</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
     </row>
@@ -616,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -629,20 +695,65 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Exames laboratoriais
+ECG
+Radiografia de tórax</t>
+        </is>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>media</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idosa com insuficiência respiratória aguda, taquicardia (HR 160) e taquipneia (RR 35) indica risco elevado e necessidade de intervenção imediata; embora não haja relato explícito de necessidade de intubação, a gravidade da dispneia justifica classificação como ESI-2, ponto B, com over‑triage aplicado por precaução.</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar necessidade de suporte ventilatório imediato (intubação ou NIPPV)
+Obter SpO2 e pressão arterial
+Avaliar nível de consciência (GCS)
+Investigar causa da descompensação (ex.: edema pulmonar, pneumonia)</t>
+        </is>
+      </c>
+      <c r="S2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -655,7 +766,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -668,20 +779,47 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta confusão, que se enquadra nos critérios de confusão/letargia/desorientação do ponto B do algoritmo ESI, indicando situação de alto risco. Não há sinais de parada cardiorrespiratória ou necessidade de intervenção imediata (ponto A). Assim, o ponto B é o primeiro satisfeito, levando à classificação ESI-2 (Emergente).</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -694,7 +832,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -707,20 +845,61 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>raio‑X de tórax
+tomografia computadorizada de tórax/abdômen/pélvis
+exames laboratoriais (hemograma, bioquímica)
+toracostomia (drenagem torácica)</t>
+        </is>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>baixa</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>O paciente sofreu trauma de alta energia com fraturas de costela e hemotórax, o que indica necessidade de múltiplos recursos diagnósticos e terapêuticos. Como não há evidência de parada cardiorrespiratória ou necessidade imediata de intervenção (Ponto A) nem de alto risco descrito nos critérios do Ponto B, avançamos ao Ponto C, estimando ≥2 recursos, o que nos leva ao Ponto D. Como os sinais vitais não foram informados, não é possível confirmar se estão na zona de perigo; aplicamos over‑triage, escolhendo o nível mais grave (ESI‑2) para garantir segurança.</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>Obter sinais vitais (PA, FC, FR, SpO2, temperatura)
+Confirmar presença ou ausência de perda de consciência no momento do acidente
+Avaliar intensidade da dor (EVA)
+Verificar necessidade de suporte ventilatório ou hemodinâmico</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -733,7 +912,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -746,20 +925,47 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>Paciente adulto apresenta febre alta, taquicardia (HR 107) e confusão, caracterizando suspeita de sepse, além de dor intensa (EVA 7) e hipoxemia (SpO2 81%). Esses achados enquadram-se nos critérios de alto risco do ponto B (sepse suspeita e alteração de consciência), exigindo avaliação emergente. Como o ponto B foi satisfeito, a classificação é ESI-2.</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -772,7 +978,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -785,20 +991,53 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+exames de imagem (TC abdômen)
+medicação intravenosa</t>
+        </is>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>Paciente apresenta hipotensão (PA 83/48) e taquicardia (HR 114), colocando seus sinais vitais na zona de perigo. Não há necessidade de intervenção imediata de ressuscitação nem critérios de alto risco descritos no ponto B. Estima-se a necessidade de pelo menos dois recursos (exames laboratoriais, imagem e medicação intravenosa). Como os sinais vitais estão na zona de perigo, o ponto D determina upgrade para ESI-2.</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -811,7 +1050,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -824,20 +1063,60 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Tomografia computadorizada de crânio (TC)
+Exames laboratoriais (hemograma, bioquímica)
+Eletrocardiograma (ECG)</t>
+        </is>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta pior dor de cabeça da vida associada a confusão, drooling e incontinência, caracterizando um quadro neurológico de alto risco. Esse conjunto de sinais ativa o ponto B (situação de alto risco/confusão), que determina classificação ESI-2 independentemente dos recursos estimados.</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>Obter sinais vitais (PA, FC, FR, SpO2, temperatura)
+Tempo de início da dor de cabeça e dos sintomas neurológicos
+Histórico de medicações em uso
+Verificar presença de hipertensão arterial descompensada ou outras comorbidades</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -850,7 +1129,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -863,20 +1142,52 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+          <t>Ressuscitação</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>Paciente de 71 anos apresenta hipotensão (85/58) e choque cardiogênico, condição que se enquadra nos critérios de choque descompensado do ponto A, exigindo intervenção imediata para salvar a vida. Assim, o ponto A foi ativado, resultando em classificação ESI-1.</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -889,7 +1200,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -902,20 +1213,56 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idoso (88 anos) com queda e uso de anticoagulante (Warfarin) enquadra‑se na regra de alto risco para idosos (queda com uso de anticoagulante) prevista no ponto B do algoritmo ESI, o que determina classificação ESI‑2 independentemente dos recursos necessários. Os sinais vitais foram descritos como críticos, reforçando a necessidade de avaliação emergente.</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>Obter valores específicos de pressão arterial, frequência cardíaca, frequência respiratória e SpO2; avaliar nível de consciência (GCS); confirmar presença de sangramento ativo ou sinais de choque; determinar necessidade de reposição de anticoagante e controle da dor; planejar exames de imagem (radiografia, tomografia) e exames laboratoriais (hemograma, coagulação).</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -928,7 +1275,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -941,20 +1288,59 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta fraqueza do lado esquerdo, queda de força na mão esquerda, queda facial direita e alteração do estado mental, caracterizando sintomas neurológicos focais agudos sugestivos de AVC, que se enquadram nos critérios de alto risco do ponto B. Como o ponto B foi satisfeito, a classificação é ESI-2, independentemente dos recursos ou sinais vitais.</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar horário exato de início dos sintomas e tempo decorrido desde o início","Realizar escala de AVC (ESC) e avaliação neurológica detalhada","Verificar INR e controle de anticoagulação por Coumadin","Considerar necessidade de imagem cerebral emergente (TC ou RM) e exames laboratoriais","Monitorar pressão arterial muito elevada e ajustar tratamento conforme protocolo"]
+disclaimer
+:
+Classificação de apoio à decisão. A avaliação final é responsabilidade do profissional de saúde.</t>
+        </is>
+      </c>
+      <c r="S10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -967,7 +1353,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -980,20 +1366,65 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>ECG
+Exames laboratoriais (troponina, hemograma)
+Cateterismo cardíaco/angioplastia</t>
+        </is>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta dor torácica típica de síndrome coronariana aguda, irradiando para braços e mandíbula, além de dispneia. Esse quadro corresponde a um critério de alto risco do ponto B do algoritmo ESI, sendo também um red flag que exige classificação mínima ESI-2. Não há evidência de parada cardiorrespiratória ou necessidade de intervenção imediata, portanto o ponto A não se aplica. Assim, o ponto B determina a classificação ESI-2 (Emergente).</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>Registrar sinais vitais (PA, FC, FR, SpO2) imediatamente
+Confirmar horário de início da dor e intensidade (EVA)
+Verificar uso de medicações prévias (ex.: nitrato, aspirina)
+Iniciar protocolo de STEMI (oxigênio, aspirina, anticoagulação)</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1006,7 +1437,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1019,20 +1450,52 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+          <t>Ressuscitação</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idosa apresenta hipotensão (90/48 mmHg) associada a bradicardia (HR 40 bpm) e sinais de hipoperfusão (letargia, oligúria, diminuição da ingestão oral), configurando choque descompensado, critério do ponto A que determina necessidade de intervenção imediata para salvar a vida, levando à classificação ESI-1.</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1045,7 +1508,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1058,20 +1521,58 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>ECG
+exames laboratoriais (troponina, hemograma, eletrólitos)
+medicação intravenosa</t>
+        </is>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idosa apresenta desconforto torácico, náuseas, vômitos e dispneia, sinais típicos de síndrome coronariana aguda, que é critério de alto risco do ponto B. Embora os sinais vitais estejam fora da zona de perigo, o quadro clínico de dor torácica suspeita justifica a classificação como ESI-2 (Emergente).</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1084,7 +1585,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1097,20 +1598,67 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>ECG
+exames laboratoriais (hemograma, eletrólitos, troponina)
+raio‑X de tórax
+medicação intravenosa (diurético)</t>
+        </is>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idosa com dor intensa (EVA 8) e sinais de alto risco (taquicardia &gt;100 bpm, taquipneia &gt;20 irpm, hipertensão) enquadra‑se nos critérios de dor intensa do ponto B, que determina classificação ESI-2. Não há necessidade de intervenção imediata (ponto A) e os critérios de alto risco justificam que a paciente não deve esperar.</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
+        <is>
+          <t>precisar confirmar duração exata da dispneia e edema
+avaliar necessidade de oxigênio suplementar apesar SpO2 100%
+verificar medicações em uso e aderência
+investigar causa da dor lombar
+obter pressão arterial invasiva ou monitorização contínua se instável</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1123,7 +1671,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1136,20 +1684,47 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>A paciente está inconsciente e apresenta contrações faciais, indicando alteração aguda do nível de consciência (GCS presumivelmente &lt;15). Esse critério corresponde ao ponto B (confusão/letargia/desorientação), que determina classificação ESI-2 independentemente de recursos ou sinais vitais. Embora a frequência cardíaca esteja acima de 100 bpm (zona de perigo), o ponto B já foi satisfeito, mantendo a classificação como ESI-2.</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1162,7 +1737,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1175,20 +1750,62 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Hemograma completo
+Teste de função hepática
+Endoscopia digestiva alta
+Transfusão de sangue</t>
+        </is>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta encefalopatia grau 1, indicando alteração aguda do nível de consciência, e apresenta hemorragia digestiva (hematêmese) associada a falha hepática aguda, caracterizando situação de alto risco. Esses achados atendem ao ponto B (alto risco/confusão), portanto a classificação mais adequada é ESI-2. Não há necessidade de intervenção imediata de ressuscitação (ponto A) e os sinais vitais estão fora da zona de perigo.</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>Resultado de exames de coagulação
+Nível plasmático de acetaminofeno
+Quantidade exata de Tylenol/ibuprofeno ingerida
+Monitoramento contínuo de pressão arterial e frequência cardíaca
+Avaliar necessidade de intubação ou suporte ventilatório</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1201,7 +1818,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1214,20 +1831,47 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta febre alta (104,6°F), taquicardia (HR 139) e pressão arterial baixa (97/54), configurando suspeita de sepse, que está listada como critério de alto risco no ponto B do algoritmo ESI. Assim, ele não deve esperar e é classificado como ESI-2 (Emergente).</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1240,7 +1884,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1253,20 +1897,53 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Exames laboratoriais (hemograma, bioquímica, cultura de fluido peritoneal)
+Imagem abdominal (raio‑X ou tomografia)
+Medicação intravenosa (antibióticos)</t>
+        </is>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta critérios de parada cardiorrespiratória, inconsciência ou choque descompensado (Ponto A) nem sinais de alto risco, confusão ou dor intensa (Ponto B). É esperado que necessite de múltiplos recursos (exames laboratoriais, imagem e antibióticos IV), portanto avançamos ao Ponto D. No Ponto D, a frequência cardíaca de 106 bpm está na zona de perigo para adultos, o que aciona a regra de upgrade para ESI-2. Assim, a classificação final é ESI-2 (Emergente).</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="S18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1279,7 +1956,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1292,20 +1969,53 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais (hemograma, coagulograma, tipagem sanguínea)
+medicação intravenosa (transfusão de sangue)
+consulta especializada (gastroenterologia/endoscopia)</t>
+        </is>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta taquicardia de 130 bpm, que está na zona de perigo para adultos, indicando risco hemodinâmico. Não há necessidade de intervenção imediata de ressuscitação (ESI-1) nem critérios de alto risco, confusão ou dor intensa (ESI-2 pelo ponto B). Estima-se a necessidade de pelo menos dois recursos (exames laboratoriais, transfusão IV e consulta especializada), o que leva ao ponto C e encaminha ao ponto D. Como os sinais vitais estão na zona de perigo, o algoritmo determina ESI-2.</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1318,7 +2028,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1331,20 +2041,61 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idosa com febre alta (102.8°F), taquicardia e letargia, além de infecção evidente no sítio da nefrostomia, caracteriza suspeita de sepse, que é critério de alto risco do ponto B; portanto a classificação mais grave ativada é o ponto B, resultando em ESI-2 (Emergente).</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>Pressão arterial e saturação de oxigênio para confirmar zona de perigo
+Avaliar necessidade de suporte hemodinâmico
+Obter culturas de sangue e urina
+Iniciar antibiótico de amplo espectro
+Considerar imagem do trato urinário
+Monitorar débito urinário e função renal</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1357,7 +2108,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1370,20 +2121,47 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta estado mental alterado (somnolência, confusão) que caracteriza alteração aguda do nível de consciência, enquadrando‑se nos critérios de alto risco do ponto B (confusão/letargia). Não há necessidade de intervenção imediata de salvamento (ponto A) e os sinais vitais não estão na zona de perigo, portanto a classificação mais apropriada é ESI-2.</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr"/>
+      <c r="S21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1409,20 +2187,47 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta dor torácica aguda com intensidade EVA 8, caracterizando dor intensa conforme o ponto B do algoritmo ESI. Não há necessidade de intervenção imediata (ponto A) e a dor intensa impede que o paciente espere, justificando a classificação ESI-2 (Emergente). Embora a frequência respiratória (RR 22) esteja na zona de perigo, a classificação já foi determinada no ponto B, permanecendo ESI-2.</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr"/>
+      <c r="S22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1438,30 +2243,69 @@
           <t>2 - Emergente</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>raio-X da coluna cervical
+raio-X torácico
+exames laboratoriais (hemograma, eletrólitos)
+ECG</t>
+        </is>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta parada cardiorrespiratória, comprometimento de via aérea ou choque, portanto o ponto A não se aplica. Não há sinais de alto risco, confusão, letargia ou dor intensa, logo o ponto B também não se aplica. Dada a queda com possível lesão vertebral/torácica, é esperado que sejam solicitados ao menos dois recursos (exames de imagem e laboratoriais, além de ECG), atendendo ao ponto C. Os sinais vitais (HR 74, RR 20, SpO2 98%) estão fora da zona de perigo, levando ao ponto D e resultando em classificação ESI-3 (urgente).</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1487,20 +2331,56 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>A paciente apresenta dor intensa de 8/10 que impede a deambulação, caracterizando dor que impede o paciente de encontrar posição confortável (critério de dor intensa do ponto B). Não há sinais de parada cardiorrespiratória, choque ou comprometimento de via aérea, portanto o ponto A não se aplica. Como o ponto B foi satisfeito, a classificação mais grave atingida é ESI-2 (Emergente).</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar presença de déficits neurológicos focais (força, sensibilidade)
+Investigar possibilidade de fratura patológica ou compressão medular (radiografia ou TC da pelve e coluna)
+Solicitar exames laboratoriais (hemograma, eletrólitos, função renal) para avaliação de infecção ou toxicidade de quimioterapia
+Avaliar necessidade de analgesia intravenosa ou bloqueio de nervo
+Obter histórico completo de medicações, alergias e comorbidades
+Monitorar sinais vitais repetidamente</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1526,20 +2406,60 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idosa (79 anos) apresenta confusão, letargia e fraqueza há 6 dias, caracterizando alteração aguda do nível de consciência. Esse quadro enquadra-se nos critérios de alto risco do ponto B (confusão/letargia/desorientação) e também nas regras de população especial para idosos com confusão mental aguda, exigindo classificação mínima ESI-2. Embora a frequência cardíaca esteja acima de 100 bpm (zona de perigo), o ponto B já determina a classificação, não sendo necessário avançar ao ponto D.</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>Identificar causa da confusão (infecção, desequilíbrio metabólico, medicações, AVC, etc.)
+Solicitar exames laboratoriais de rotina e gasometria arterial
+Considerar ECG e avaliação neurológica de urgência
+Obter histórico completo de comorbidades, medicações em uso e uso de anticoagulantes
+Monitorar sinais vitais de forma contínua</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1565,20 +2485,66 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>ECG
+Exames laboratoriais (troponina, hemograma, bioquímica)
+Radiografia de tórax</t>
+        </is>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>media</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="N26" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta sincope e histórico de dor torácica recorrente em contexto de CAD, hipertensão e outras comorbidades cardiovasculares, o que caracteriza situação de alto risco segundo o ponto B do algoritmo ESI. Embora os sinais vitais estejam fora da zona de perigo, a presença de possível síndrome coronariana aguda justifica a classificação como ESI-2. Como há dúvida sobre a gravidade exata (sincope sem dor atual), aplicou‑se over‑triage, escolhendo o nível mais grave.</t>
+        </is>
+      </c>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar presença ou ausência de dor torácica no momento da avaliação
+Obter ECG imediatamente
+Avaliar causa da síncope (cardíaca, ortostática, neurológica)
+Revisar medicações em uso (prednisona, anti-hipertensivos)
+Monitorar sinais vitais de forma contínua</t>
+        </is>
+      </c>
+      <c r="S26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1604,20 +2570,52 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+exames de imagem (ultrassonografia abdominal)</t>
+        </is>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta necessidade de intervenção imediata (ponto A) nem se enquadra nos critérios de alto risco, confusão ou dor intensa (ponto B). Estima‑se que precisará de pelo menos dois recursos (exames laboratoriais e imagem), o que encaminha ao ponto D. Na avaliação dos sinais vitais, a frequência respiratória está acima de 20 irpm, caracterizando zona de perigo; assim, o ponto D determina classificação ESI-2.</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="inlineStr"/>
+      <c r="S27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1643,20 +2641,52 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>media</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="N28" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta dor torácica nova, diferente da angina prévia, em contexto de doença cardíaca grave e idade avançada, o que se enquadra nos critérios de alto risco do ponto B. Não há necessidade de intervenção imediata (ponto A) e os sinais vitais estão fora da zona de perigo. Assim, o ponto B determina classificação ESI-2.</t>
+        </is>
+      </c>
+      <c r="R28" s="4" t="inlineStr"/>
+      <c r="S28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1682,20 +2712,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>A paciente apresenta dor flank intensa com EVA 10, que se enquadra nos critérios de dor intensa do ponto B (EVA ≥7). Não há necessidade de intervenção imediata (ponto A) nem outros critérios de alto risco. Assim, o ponto B é o primeiro satisfeito, resultando na classificação ESI-2 (Emergente).</t>
+        </is>
+      </c>
+      <c r="R29" s="4" t="inlineStr"/>
+      <c r="S29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1721,20 +2778,58 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais (hemograma, bioquímica, coagulograma)
+infusão intravenosa de fluidos
+consulta gastroenterológica</t>
+        </is>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta critérios de parada cardiorrespiratória nem necessidade de intervenção imediata (Ponto A). Não há sinais de alto risco, confusão ou dor intensa que justifiquem ESI-2 pelo Ponto B. O quadro de sangramento retal provavelmente demandará múltiplos recursos (exames laboratoriais, reposição intravenosa e consulta especializada), configurando ≥2 recursos e encaminhando ao Ponto D. Os sinais vitais mostram frequência cardíaca de 101 bpm, que está na zona de perigo, ativando o Ponto D e resultando em classificação ESI-2.</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="inlineStr"/>
+      <c r="S30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1760,20 +2855,57 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>CT de crânio
+exames laboratoriais</t>
+        </is>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idosa (65 anos) sofreu queda com golpe na cabeça, o que, segundo as regras especiais para idosos, caracteriza risco elevado (queda com trauma craniano) e exige classificação mínima ESI-2. Não há sinais vitais na zona de perigo, mas a presença do trauma craniano em idoso ativa o ponto B do algoritmo, levando ao escalonamento emergente.</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr"/>
+      <c r="S31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1789,30 +2921,76 @@
           <t>2 - Emergente</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais (hemograma, bioquímica, troponina)
+raio‑X de tórax
+eletrocardiograma</t>
+        </is>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta parada cardiorrespiratória nem necessidade de intervenção imediata (Ponto A). Não há critérios de alto risco, confusão, letargia ou dor intensa que justifiquem ESI‑2 (Ponto B). Foram identificados pelo menos dois recursos necessários (exames laboratoriais, raio‑X e ECG), o que encaminha ao Ponto D. As constantes vitais (PA 161/92, FC 92, FR 19, SpO2 100%) estão fora da zona de perigo, portanto a classificação final é ESI‑3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>quantificar a quantidade e frequência de fezes escuras (possível sangramento gastrointestinal)
+verificar uso de anticoagulantes ou antiagregantes plaquetários
+obter hemoglobina e hematócrito
+avaliar necessidade de monitoramento cardíaco contínuo
+investigar causa da dispneia de esforço prolongada</t>
+        </is>
+      </c>
+      <c r="S32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1828,30 +3006,76 @@
           <t>2 - Emergente</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais (hemograma, bioquímica)
+medicação intravenosa (antibiótico)
+ultrassonografia de membros inferiores</t>
+        </is>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idoso apresenta edema e eritema no membro inferior, sem dor, sem sinais vitais de perigo e sem confusão ou dor intensa. Não há critérios de alto risco do ponto B, portanto avançamos ao ponto C, estimando necessidade de múltiplos recursos (exames laboratoriais, antibiótico IV e ultrassom). Como são ≥2 recursos, passamos ao ponto D; os sinais vitais estão dentro da zona normal, resultando em classificação ESI-3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar presença de febre, calafrios ou sinais de sepse
+Determinar duração e evolução do edema e vermelhidão
+Avaliar dor ou sensibilidade local
+Considerar cultura de sangue e de exsudato
+Monitorar pressão arterial e frequência cardíaca serialmente</t>
+        </is>
+      </c>
+      <c r="S33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1877,20 +3101,52 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais (hemograma, bioquímica, gasometria)
+raio‑X de tórax</t>
+        </is>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta dispneia e hipoxemia, mas não está em parada cardiorrespiratória nem requer intubação imediata (Ponto A negativo). Não há confusão, dor intensa ou condições de alto risco listadas (Ponto B negativo). Estima‑se a necessidade de pelo menos dois recursos (exames laboratoriais e radiografia de tórax), encaminhando ao Ponto C e, subsequentemente, ao Ponto D. Os sinais vitais mostram frequência cardíaca de 116 bpm, que está na zona de perigo (&gt;100 bpm), ativando o critério do Ponto D e resultando na classificação ESI‑2.</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr"/>
+      <c r="S34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1906,30 +3162,63 @@
           <t>2 - Emergente</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+consulta psiquiátrica
+consulta nutricional</t>
+        </is>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta necessidade de intervenção imediata (Ponto A) nem critérios de alto risco, confusão ou dor intensa (Ponto B). Estima-se que precisará de pelo menos dois recursos (exames laboratoriais, consultas especializadas), o que encaminha ao Ponto D. Seus sinais vitais estão dentro dos limites normais, portanto não há zona de perigo, resultando em classificação ESI-3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R35" s="4" t="inlineStr"/>
+      <c r="S35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1945,30 +3234,63 @@
           <t>2 - Emergente</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+medicação intravenosa (antibiótico)
+exame de imagem (raio‑X ou tomografia)</t>
+        </is>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta parada cardiorrespiratória nem necessidade de intervenção imediata (Ponto A). Não há sinais de alto risco, confusão, letargia ou dor intensa (Ponto B). Com base no quadro clínico, é provável que sejam necessários pelo menos dois recursos (exames laboratoriais, medicação IV e imagem), encaminhando ao Ponto D. Os sinais vitais (HR 84, RR 16, SpO2 98%, T 98,2°F) estão dentro dos limites normais, portanto não estão na zona de perigo, resultando em classificação ESI-3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R36" s="4" t="inlineStr"/>
+      <c r="S36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1994,20 +3316,53 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+raio‑X de tórax
+nebulização</t>
+        </is>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>Paciente adulta com dispneia grave, mas mantém fala completa. Não há parada cardiorrespiratória nem necessidade de intervenção imediata (Ponto A). Não apresenta alto risco definido, confusão ou dor intensa (Ponto B). Necessitará de pelo menos dois recursos (laboratoriais, imagem e nebulização), encaminhando ao Ponto C e, ao chegar ao Ponto D, a frequência respiratória de 25 está na zona de perigo, o que eleva a classificação para ESI‑2.</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr"/>
+      <c r="S37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2023,30 +3378,68 @@
           <t>2 - Emergente</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais (hemograma, bioquímica hepática)
+exame de imagem (ultrassonografia ou tomografia abdominal)
+consulta especializada (gastroenterologia)</t>
+        </is>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
           <t>media</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1</v>
-      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta critérios de parada cardiorrespiratória nem sinais de alto risco (dor intensa, confusão, choque, etc.), portanto os pontos A e B não foram ativados. Ele provavelmente necessitará múltiplos recursos (exames laboratoriais, imagem e consulta especializada), o que leva ao ponto C com ≥2 recursos, encaminhando ao ponto D. Seus sinais vitais (HR 58, RR 18, SpO2 98%) estão fora da zona de perigo, resultando em classificação ESI-3 (urgente).</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="inlineStr"/>
+      <c r="S38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2072,20 +3465,47 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta dor abdominal intensa (EVA 8), que se enquadra nos critérios de dor intensa do ponto B. Esse critério ativa a classificação ESI-2, indicando situação emergente que não requer intervenção imediata, mas demanda avaliação rápida. Embora os sinais vitais apresentem frequência cardíaca acima de 100 bpm (zona de perigo), o ponto B já determina a classificação mais alta antes de avaliar recursos ou zona de perigo adicional.</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="inlineStr"/>
+      <c r="S39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2111,20 +3531,52 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta confusão mental aguda (desorientação quanto à data de nascimento e ao presidente) e dificuldade de fala, caracterizando alteração aguda do nível de consciência. De acordo com o ponto B do algoritmo ESI, situações de alto risco incluem confusão/letargia/desorientação, especialmente em idosos, o que impede que o paciente espere. Portanto, o ponto B é o primeiro satisfeito, levando à classificação ESI-2 (Emergente).</t>
+        </is>
+      </c>
+      <c r="R40" s="4" t="inlineStr"/>
+      <c r="S40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2150,20 +3602,52 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idoso (77 anos) chegou após convulsão generalizada, agora em estado pós‑ictal drowsy, o que caracteriza alteração aguda do nível de consciência, critério de alto risco do ponto B. Não há necessidade de intervenção imediata (ponto A). Assim, o ponto B é o primeiro satisfeito, levando à classificação ESI‑2. Os sinais vitais mostram frequência cardíaca 111 bpm, dentro da zona de perigo, reforçando a necessidade de atenção emergente.</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="inlineStr"/>
+      <c r="S41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2171,7 +3655,7 @@
           <t>30031158</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -2179,30 +3663,63 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>imagem (ultrassom ou TC facial)
+exames laboratoriais (hemograma)
+incisão e drenagem (procedimento)</t>
+        </is>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>Paciente adulto sem sinais de vida ameaçados (ponto A negativo) e sem critérios de alto risco, confusão ou dor intensa (ponto B negativo). Necessita de mais de um recurso (imagem, exames laboratoriais e procedimento de drenagem), portanto avançamos ao ponto D. Os sinais vitais estão dentro dos limites normais, não configurando zona de perigo, o que determina classificação ESI-3 (urgente).</t>
+        </is>
+      </c>
+      <c r="R42" s="4" t="inlineStr"/>
+      <c r="S42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2210,7 +3727,7 @@
           <t>30007072</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -2218,30 +3735,62 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais (hemograma, bioquímica)
+raio‑X de tórax</t>
+        </is>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N43" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta parada cardiorrespiratória nem necessidade de intervenção imediata (Ponto A). Não há critérios de alto risco, confusão ou dor intensa que justifiquem ESI-2 (Ponto B). Estima‑se a necessidade de pelo menos dois recursos (exames laboratoriais e raio‑X de tórax), encaminhando ao Ponto C e, consequentemente, ao Ponto D. Os sinais vitais (PA 162/98, FC 76, FR 20, SpO2 96%) estão fora da zona de perigo, portanto a classificação final é ESI-3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R43" s="4" t="inlineStr"/>
+      <c r="S43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2249,7 +3798,7 @@
           <t>30075158</t>
         </is>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -2257,30 +3806,74 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>ESI-4</t>
         </is>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais</t>
+        </is>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
           <t>baixa</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idosa com fraqueza generalizada, sem dor, sem sinais de alto risco ou necessidade de intervenção imediata. Os sinais vitais foram descritos como estáveis, mas não foram fornecidos valores específicos, impossibilitando avaliação de zona de perigo. Considerando a fraqueza, é provável que sejam solicitados exames laboratoriais para investigação, configurando a necessidade de um recurso. Não há indicação de necessidade de dois ou mais recursos, portanto o ponto C indica ESI-4. Devido à falta de informações detalhadas (valores de sinais vitais, estado mental, duração da fraqueza, comorbidades), aplicou‑se over‑triage, escolhendo o nível mais grave entre ESI-4 e ESI-5, com confiança baixa.</t>
+        </is>
+      </c>
+      <c r="R44" s="4" t="inlineStr">
+        <is>
+          <t>Obter valores de pressão arterial, frequência cardíaca, frequência respiratória e SpO2
+Avaliar nível de consciência (GCS) e presença de confusão ou letargia
+Determinar duração e início da fraqueza
+Investigar comorbidades e medicações em uso
+Considerar necessidade de ECG ou outros exames de imagem</t>
+        </is>
+      </c>
+      <c r="S44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2288,7 +3881,7 @@
           <t>30406785</t>
         </is>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -2306,20 +3899,61 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+ECG
+ultrassonografia abdominal</t>
+        </is>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
           <t>baixa</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta critérios de parada cardiorrespiratória nem necessidade de intervenção imediata (Ponto A). Não há sinais de alto risco, confusão ou dor intensa no momento (Ponto B). Foram estimados pelo menos dois recursos (laboratoriais, ECG e imagem), o que encaminha ao Ponto D. Como os sinais vitais não foram informados, há dúvida sobre a presença de parâmetros na zona de perigo; aplicou‑se over‑triage, classificando como ESI-2 para garantir segurança.</t>
+        </is>
+      </c>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>obter sinais vitais (PA, FC, FR, SpO2, temperatura)
+duração e início da dor abdominal
+presença de icterícia ou alterações de pele
+exame físico abdominal detalhado
+história de doenças hepáticas ou biliares</t>
+        </is>
+      </c>
+      <c r="S45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2327,7 +3961,7 @@
           <t>30821723</t>
         </is>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -2335,30 +3969,62 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+ECG</t>
+        </is>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>Paciente adulta estável, sem dor, sem confusão e sem sinais de alto risco, não atendendo aos critérios dos pontos A ou B. Estima-se a necessidade de pelo menos dois recursos (exames laboratoriais e ECG) para avaliação de sua cirrose, hipertensão e sopro cardíaco, o que encaminha ao ponto D. Seus sinais vitais (FC 91 bpm, FR 16 irpm, SpO2 100%) estão fora da zona de perigo, permitindo classificação como ESI-3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R46" s="4" t="inlineStr"/>
+      <c r="S46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2366,7 +4032,7 @@
           <t>30918085</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -2374,30 +4040,62 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+raio‑X ou tomografia</t>
+        </is>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N47" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1</v>
-      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta risco de vida imediato (Ponto A) nem critérios de alto risco, confusão ou dor intensa (Ponto B). Os sinais vitais estão dentro dos limites normais, mas a queda mecânica provavelmente exigirá ao menos dois recursos (exames laboratoriais e imagem). Como há ≥2 recursos estimados, avançamos ao Ponto D; os sinais vitais não estão na zona de perigo, levando à classificação ESI-3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R47" s="4" t="inlineStr"/>
+      <c r="S47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2405,7 +4103,7 @@
           <t>39914411</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2413,30 +4111,63 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+medicação intravenosa
+imagem (ultrassom)</t>
+        </is>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta critérios de risco imediato (Ponto A) nem sinais de alto risco, confusão ou dor intensa (Ponto B). Estima-se a necessidade de pelo menos dois recursos (exames laboratoriais, antibiótico IV e possível ultrassom), o que encaminha ao Ponto D. Seus sinais vitais (FC 69, FR 18, SpO2 96%) estão fora da zona de perigo, portanto a classificação final é ESI-3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R48" s="4" t="inlineStr"/>
+      <c r="S48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2444,7 +4175,7 @@
           <t>30191707</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -2462,20 +4193,47 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
+      <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta dor de perna direita com intensidade EVA 8/10, atendendo ao critério de dor intensa do ponto B (EVA ≥7). Não há sinais de parada cardiorrespiratória nem necessidade de intervenção imediata (ponto A). Assim, o ponto B é o primeiro satisfeito, levando à classificação ESI-2 (Emergente).</t>
+        </is>
+      </c>
+      <c r="R49" s="4" t="inlineStr"/>
+      <c r="S49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2483,7 +4241,7 @@
           <t>30193081</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -2491,30 +4249,62 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Raio‑X da extremidade inferior
+Imobilização/splintagem</t>
+        </is>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>Paciente jovem, ambulante, com dor moderada (EVA 6) e sem sinais de alto risco ou confusão. Não há necessidade de intervenção imediata (Ponto A) nem critérios de alto risco ou dor intensa (Ponto B). Estima‑se a necessidade de pelo menos dois recursos (raio‑X e imobilização), ativando o Ponto C e, consequentemente, o Ponto D. Os sinais vitais estão dentro dos limites normais, portanto não há zona de perigo, resultando em classificação ESI‑3 (urgente).</t>
+        </is>
+      </c>
+      <c r="R50" s="4" t="inlineStr"/>
+      <c r="S50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2522,7 +4312,7 @@
           <t>32258048</t>
         </is>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -2530,30 +4320,71 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+exame de imagem (TC ou ultrassom)</t>
+        </is>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N51" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta critérios de risco imediato (ponto A) nem sinais de alto risco, confusão ou dor intensa (ponto B). Os sinais vitais estão dentro da normalidade, portanto não há zona de perigo. Considerando a dor abdominal e a necessidade provável de investigação diagnóstica, estima-se a necessidade de pelo menos dois recursos (exames laboratoriais e imagem), o que encaminha ao ponto D, onde os sinais vitais são estáveis, resultando em classificação ESI-3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>Duração e início da dor abdominal
+Presença de febre, náuseas ou vômitos
+Histórico ginecológico (menstruação, possibilidade de gravidez)
+Alterações urinárias (disúria, hematuria)
+Histórico de doenças crônicas ou medicações em uso
+Exame físico detalhado (sensibilidade, rigidez)</t>
+        </is>
+      </c>
+      <c r="S51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2561,7 +4392,7 @@
           <t>35664211</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -2579,20 +4410,59 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>raio-X
+exames laboratoriais</t>
+        </is>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta parada cardiorrespiratória nem necessidade de intervenção imediata (Ponto A). Não há critérios de alto risco, confusão, letargia ou dor intensa que justifiquem ESI-2 pelo Ponto B. O mecanismo de queda sugere necessidade de ao menos dois recursos (ex.: raio‑X para avaliação de fraturas e exames laboratoriais), encaminhando ao Ponto D. Os sinais vitais mostram frequência cardíaca de 104 bpm, que está acima do limite superior da zona de perigo (HR&gt;100), ativando o critério de zona de perigo e, portanto, a classificação é upgrade para ESI-2.</t>
+        </is>
+      </c>
+      <c r="R52" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar presença de dor ou sensibilidade local
+Avaliar déficits neurológicos ou sinais de lesão interna
+Determinar necessidade de imobilização ou sutura
+Obter histórico completo de medicações e comorbidades</t>
+        </is>
+      </c>
+      <c r="S52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2600,7 +4470,7 @@
           <t>36327718</t>
         </is>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -2608,30 +4478,62 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="E53" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Eletrocardiograma (ECG)
+Exames laboratoriais (hemograma, bioquímica)</t>
+        </is>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta tontura sem dor, sem sinais de alto risco (ponto B) e está hemodinamicamente estável (sinais vitais normais). Não há necessidade de intervenção imediata (ponto A). Estima‑se a necessidade de pelo menos dois recursos (ECG e exames laboratoriais), ativando o ponto C e, consequentemente, o ponto D. Como os sinais vitais não estão na zona de perigo, a classificação final é ESI‑3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R53" s="4" t="inlineStr"/>
+      <c r="S53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2639,7 +4541,7 @@
           <t>30022323</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -2657,20 +4559,60 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+exame de imagem (ultrassom ou tomografia)</t>
+        </is>
+      </c>
+      <c r="J54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>Paciente com dor abdominal moderada (EVA 5) não apresenta critérios de alto risco nem confusão, portanto não se enquadra nos pontos A ou B. É esperado que necessite de pelo menos dois recursos (exames laboratoriais e imagem), levando ao ponto C e, consequentemente, ao ponto D. O pulso está em 105 bpm, acima de 100 bpm, caracterizando zona de perigo; assim, a classificação é ESI-2.</t>
+        </is>
+      </c>
+      <c r="R54" s="4" t="inlineStr">
+        <is>
+          <t>duração e início da dor abdominal
+presença de náuseas, vômitos ou alterações intestinais
+história de doenças prévias e medicações em uso
+possível gravidez
+sinais de peritonite ou sangramento interno</t>
+        </is>
+      </c>
+      <c r="S54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2678,7 +4620,7 @@
           <t>30025651</t>
         </is>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -2686,30 +4628,62 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="E55" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>urinalise
+urine culture</t>
+        </is>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N55" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta critérios de parada cardiorrespiratória nem necessidade de intervenção imediata (Ponto A). Não há sinais de alto risco, confusão, letargia ou dor intensa (EVA 5) que caracterizem o Ponto B. Estima‑se a necessidade de pelo menos dois recursos (ex.: urinalise e cultura de urina) para investigação da disúria e dor pélvica, acionando o Ponto C e levando ao Ponto D. Os sinais vitais (FC 95, FR 18, SpO2 94%, PA 105/56, temperatura 97.6°F) estão fora da zona de perigo, portanto a classificação final é ESI‑3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R55" s="4" t="inlineStr"/>
+      <c r="S55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2717,7 +4691,7 @@
           <t>30061072</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -2725,30 +4699,62 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E56" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+exame de imagem (ultrassonografia ou tomografia)</t>
+        </is>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N56" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta dor abdominal de baixa intensidade (EVA 2) sem sinais de alto risco, confusão ou dor intensa. Não há critérios do ponto A (nenhum comprometimento de vida) nem do ponto B (sem dor torácica, AVC, intoxicação, etc.). Estima-se a necessidade de pelo menos dois recursos (exames laboratoriais e imagem), o que encaminha ao ponto D. Os sinais vitais (FC 76, FR 16, SpO2 98%) estão fora da zona de perigo, portanto a classificação final é ESI-3 (urgente).</t>
+        </is>
+      </c>
+      <c r="R56" s="4" t="inlineStr"/>
+      <c r="S56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2756,7 +4762,7 @@
           <t>30075347</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -2764,30 +4770,62 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E57" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+consulta especializada/colonoscopia</t>
+        </is>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N57" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta risco de vida imediato (Ponto A) nem critérios de alto risco, confusão ou dor intensa (Ponto B). Com base no quadro de sangramento retal e diarreia, é esperado que sejam solicitados exames laboratoriais e uma avaliação especializada (colonoscopia ou consulta de gastroenterologia), totalizando dois ou mais recursos, o que aciona o Ponto C e encaminha ao Ponto D. Os sinais vitais (PA 135/81, FC 79, FR 16, SpO2 100) estão fora da zona de perigo, portanto a classificação final é ESI-3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R57" s="4" t="inlineStr"/>
+      <c r="S57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2795,7 +4833,7 @@
           <t>30145934</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -2803,30 +4841,70 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E58" s="6" t="n">
+      <c r="E58" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>exames laboratoriais
+exame de imagem (TC ou ultrassom)</t>
+        </is>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N58" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta dor abdominal moderada (EVA 5) sem sinais de alto risco, confusão ou dor intensa. Não há critérios do ponto A (nenhum comprometimento vital) nem do ponto B (sem dor severa, sem confusão, sem risco imediato). Os sinais vitais estão dentro dos limites normais, portanto não há zona de perigo. Estima-se a necessidade de pelo menos dois recursos (exames laboratoriais e imagem), o que aciona o ponto D. Como os sinais vitais não estão na zona de perigo, a classificação final é ESI-3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>Duração e início da dor abdominal
+Presença de náuseas, vômitos, alterações urinárias ou sangramento
+Histórico médico prévio, medicações em uso e alergias
+Exame físico detalhado (sensibilidade, rigidez, massa)
+Temperatura em escala Celsius para confirmar ausência de febre</t>
+        </is>
+      </c>
+      <c r="S58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2834,7 +4912,7 @@
           <t>30220886</t>
         </is>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -2842,30 +4920,75 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E59" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>hemograma completo
+raio‑X de tórax</t>
+        </is>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
           <t>media</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="N59" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta necessidade de ressuscitação (Ponto A) nem critérios de alto risco, confusão ou dor intensa (Ponto B). Estima‑se que precisará de pelo menos dois recursos (exames laboratoriais e imagem), o que encaminha ao Ponto D. Seus sinais vitais (FC 80, FR 16, SpO2 98) estão fora da zona de perigo, portanto a classificação final é ESI-3 (Urgente).</t>
+        </is>
+      </c>
+      <c r="R59" s="4" t="inlineStr">
+        <is>
+          <t>duração da febre
+presença de sintomas associados (tosse, dor torácica, dor abdominal)
+comorbidades pré‑existentes
+medicações em uso
+pressão arterial diastólica baixa – necessidade de monitoramento</t>
+        </is>
+      </c>
+      <c r="S59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2873,7 +4996,7 @@
           <t>30267864</t>
         </is>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -2881,30 +5004,63 @@
           <t>3 - Urgente</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E60" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>3</v>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>ECG
+raio‑X de tórax
+exames laboratoriais</t>
+        </is>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N60" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta falta de ar, mas está consciente, com sinais vitais dentro dos limites normais (FC 79, FR 20, SpO2 100%). Não há critérios de risco imediato (ponto A) nem de alto risco, confusão ou dor intensa (ponto B). Estima‑se a necessidade de pelo menos dois recursos (ECG e raio‑X de tórax, além de exames laboratoriais), o que encaminha ao ponto D. Como os sinais vitais não estão na zona de perigo, a classificação final é ESI‑3 (urgente).</t>
+        </is>
+      </c>
+      <c r="R60" s="4" t="inlineStr"/>
+      <c r="S60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2912,7 +5068,7 @@
           <t>30291238</t>
         </is>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -2930,20 +5086,61 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="4" t="inlineStr"/>
+      <c r="J61" t="b">
+        <v>1</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L61" t="b">
+        <v>1</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
           <t>media</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1</v>
-      </c>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>Paciente idoso (67 anos) apresenta tosse e letargia. Embora não haja parada cardiorrespiratória nem necessidade de intervenção imediata (Ponto A), a presença de letargia pode ser considerada letargia significativa, enquadrando‑se nos critérios de alto risco/confusão do Ponto B. Além disso, a frequência respiratória de 22 irpm está na zona de perigo, reforçando a necessidade de avaliação urgente. Assim, o algoritmo aciona o Ponto B, resultando em classificação ESI-2. Devido à dúvida sobre a gravidade da letargia, aplicou‑se over‑triage para garantir segurança.</t>
+        </is>
+      </c>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>Qual é o nível de consciência atual (GCS)?
+Existe febre ou outros sinais de infecção?
+Histórico de doença pulmonar crônica (COPD, asma) ou outras comorbidades?
+Uso de medicações atuais, especialmente broncodilatadores ou corticoides?
+Duração e evolução dos sintomas (tosse, letargia)?
+Exame físico respiratório (ausculta, esforço respiratório)</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2951,7 +5148,7 @@
           <t>30202377</t>
         </is>
       </c>
-      <c r="B62" s="7" t="n">
+      <c r="B62" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -2959,30 +5156,62 @@
           <t>4 - Menos urgente</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>raio‑X do pé
+imobilização (splint)</t>
+        </is>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>A paciente apresenta lesão no pé com dor moderada (EVA 5) e sinais vitais estáveis, não há risco imediato de vida nem critérios de alto risco ou dor intensa. Estima‑se a necessidade de pelo menos dois recursos (imagem radiográfica e imobilização), atendendo ao critério do ponto C (≥2 recursos). Os sinais vitais não se encontram na zona de perigo, portanto, no ponto D a classificação permanece ESI‑3 (urgente).</t>
+        </is>
+      </c>
+      <c r="R62" s="4" t="inlineStr"/>
+      <c r="S62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2990,7 +5219,7 @@
           <t>30520442</t>
         </is>
       </c>
-      <c r="B63" s="7" t="n">
+      <c r="B63" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -2998,30 +5227,62 @@
           <t>4 - Menos urgente</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E63" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>raio‑X do punho
+imobilização/splintagem</t>
+        </is>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta risco de vida imediato nem critérios de alto risco (ponto A e B). Foram estimados dois recursos necessários (raio‑X e imobilização), o que encaminha ao ponto D. Os sinais vitais (PA 156/88, pulso 56, frequência respiratória 18, SpO2 97%) estão fora da zona de perigo, permitindo classificação como ESI‑3 (urgente).</t>
+        </is>
+      </c>
+      <c r="R63" s="4" t="inlineStr"/>
+      <c r="S63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3029,7 +5290,7 @@
           <t>32233858</t>
         </is>
       </c>
-      <c r="B64" s="7" t="n">
+      <c r="B64" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -3037,30 +5298,61 @@
           <t>4 - Menos urgente</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>ESI-4</t>
         </is>
       </c>
-      <c r="E64" s="7" t="n">
+      <c r="E64" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>sutura</t>
+        </is>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N64" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta critérios do ponto A (nenhum risco de vida imediato) nem do ponto B (não há dor intensa, confusão, letargia ou condição de alto risco). Os sinais vitais estão dentro da normalidade, portanto não há zona de perigo. Para a lacerção, o recurso esperado é a sutura, que conta como um único procedimento. Como a necessidade estimada é de exatamente 1 recurso, o algoritmo indica ESI-4 (Menos urgente).</t>
+        </is>
+      </c>
+      <c r="R64" s="4" t="inlineStr"/>
+      <c r="S64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3068,7 +5360,7 @@
           <t>32745877</t>
         </is>
       </c>
-      <c r="B65" s="7" t="n">
+      <c r="B65" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -3086,20 +5378,51 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>Raio‑X do tornozelo</t>
+        </is>
+      </c>
+      <c r="J65" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="4" t="inlineStr">
+        <is>
+          <t>O paciente apresenta dor intensa no tornozelo com EVA 7, que se enquadra nos critérios de dor intensa do ponto B (dor EVA ≥ 7/10). Não há sinais de parada cardiorrespiratória ou necessidade de intervenção imediata (ponto A). Assim, o ponto B é o primeiro satisfeito, levando à classificação ESI-2 (Emergente). Os sinais vitais mostram frequência cardíaca de 106 bpm, que está na zona de perigo, mas isso reforça a necessidade de atenção, sem alterar a classificação já definida pelo ponto B.</t>
+        </is>
+      </c>
+      <c r="R65" s="4" t="inlineStr"/>
+      <c r="S65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3107,7 +5430,7 @@
           <t>32925431</t>
         </is>
       </c>
-      <c r="B66" s="7" t="n">
+      <c r="B66" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -3115,30 +5438,61 @@
           <t>4 - Menos urgente</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>ESI-4</t>
         </is>
       </c>
-      <c r="E66" s="7" t="n">
+      <c r="E66" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>sutura</t>
+        </is>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N66" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta risco de vida imediato (Ponto A) nem sinais de alto risco, confusão ou dor intensa (Ponto B). A lesão descrita (laceração do polegar) requer apenas um recurso, a sutura, sem necessidade de exames laboratoriais, de imagem ou medicação intravenosa. Assim, no Ponto C a estimativa é de 1 recurso, o que classifica o caso como ESI-4 (Menos urgente).</t>
+        </is>
+      </c>
+      <c r="R66" s="4" t="inlineStr"/>
+      <c r="S66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3146,38 +5500,2417 @@
           <t>30466164</t>
         </is>
       </c>
-      <c r="B67" s="8" t="n">
+      <c r="B67" s="9" t="n">
         <v>5</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>5 - Não urgente</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>ESI-4</t>
         </is>
       </c>
-      <c r="E67" s="7" t="n">
+      <c r="E67" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>consulta oftalmológica</t>
+        </is>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>O paciente não apresenta risco de vida imediato (Ponto A) nem critérios de alto risco, confusão ou dor intensa (Ponto B). Os sinais vitais estão dentro dos limites normais, portanto não há zona de perigo. Estima-se que será necessário apenas um recurso, como consulta oftalmológica ou exame com lâmpada de fenda, caracterizando 1 recurso (Ponto C) e levando à classificação ESI-4 (Menos urgente).</t>
+        </is>
+      </c>
+      <c r="R67" s="4" t="inlineStr"/>
+      <c r="S67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>31856073</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>ESI-2</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>raio-x do tornozelo
+analgesia IV</t>
+        </is>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="4" t="inlineStr">
+        <is>
+          <t>dor intensa (EVA 8) → ponto B → classificação ESI-2</t>
+        </is>
+      </c>
+      <c r="R68" s="4" t="inlineStr"/>
+      <c r="S68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>31864066</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>raio-x do joelho</t>
+        </is>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="4" t="inlineStr">
+        <is>
+          <t>Dor de intensidade moderada (EVA 4) sem sinais de risco ou red flags, paciente ambulatório e sinais vitais normais → ponto C ativado, necessidade de 1 recurso (imagem) → classificação ESI-4</t>
+        </is>
+      </c>
+      <c r="R69" s="4" t="inlineStr"/>
+      <c r="S69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>31990620</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>sutura</t>
+        </is>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N70" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="4" t="inlineStr">
+        <is>
+          <t>Queixa de mordida de cachorro sem dor, sinais vitais estáveis e sem red flags; não atende aos critérios de ESI-1 ou ESI-2; requer apenas um recurso (ex.: sutura), portanto ponto C indica 1 recurso → classificação ESI-4.</t>
+        </is>
+      </c>
+      <c r="R70" s="4" t="inlineStr"/>
+      <c r="S70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>32177938</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>imagem (raio‑x do joelho)</t>
+        </is>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="4" t="inlineStr">
+        <is>
+          <t>Dor leve (EVA 1), sem sinais de gravidade, sinais vitais estáveis e sem red flags. Necessita apenas de um recurso (raio‑x do joelho), portanto ponto C com 1 recurso → classificação ESI‑4.</t>
+        </is>
+      </c>
+      <c r="R71" s="4" t="inlineStr"/>
+      <c r="S71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>32378986</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>ESI-2</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="4" t="inlineStr">
+        <is>
+          <t>Dor ocular intensa (EVA 8) atende ao critério de dor intensa do ponto B, que determina classificação ESI-2. Não há sinais vitais na zona de perigo nem red flags que justifiquem ESI-1. Portanto, a classificação é ESI-2.</t>
+        </is>
+      </c>
+      <c r="R72" s="4" t="inlineStr"/>
+      <c r="S72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>32660151</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>raio‑x do pé/toe</t>
+        </is>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N73" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>Dor moderada (EVA 6) sem sinais de risco, vitais estáveis, necessidade de apenas um recurso (raio‑x), portanto ponto C com 1 recurso → ESI‑4</t>
+        </is>
+      </c>
+      <c r="R73" s="4" t="inlineStr"/>
+      <c r="S73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>32829045</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>ESI-2</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>imagem (raio‑x)</t>
+        </is>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="4" t="inlineStr">
+        <is>
+          <t>Dor de intensidade 7/10 caracteriza dor intensa, atendendo ao critério do ponto B; portanto a classificação é ESI-2.</t>
+        </is>
+      </c>
+      <c r="R74" s="4" t="inlineStr"/>
+      <c r="S74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>33657421</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Não urgente</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="4" t="inlineStr"/>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="4" t="inlineStr">
+        <is>
+          <t>Sintomas de síndrome das pernas inquietas sem dor, sem sinais de risco ou red flags; sinais vitais normais; nenhum recurso imediato necessário → ponto C com 0 recursos → classificação ESI-5.</t>
+        </is>
+      </c>
+      <c r="R75" s="4" t="inlineStr"/>
+      <c r="S75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>34058541</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>sutura</t>
+        </is>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="4" t="inlineStr">
+        <is>
+          <t>Laceração da mão sem dor, sinais vitais estáveis e sem critérios de ESI-1 ou ESI-2; requer apenas sutura (1 recurso) → ponto C → classificação ESI-4</t>
+        </is>
+      </c>
+      <c r="R76" s="4" t="inlineStr"/>
+      <c r="S76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>34723477</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>ESI-2</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>imagem (raio‑x)
+medicação IV
+procedimento (imobilização)</t>
+        </is>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="4" t="inlineStr">
+        <is>
+          <t>Paciente relata dor de 8/10 na extremidade inferior, caracterizando dor intensa (EVA ≥7). Esse critério satisfaz o ponto B do algoritmo ESI, que direciona a classificação para ESI-2. Não há sinais vitais na zona de perigo nem red flags que justifiquem ESI-1.</t>
+        </is>
+      </c>
+      <c r="R77" s="4" t="inlineStr"/>
+      <c r="S77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>34791387</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>sutura</t>
+        </is>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="4" t="inlineStr">
+        <is>
+          <t>A lesão é uma laceração de dedo com dor moderada (EVA 4) e sem sinais de comprometimento vital ou red flags. Não atende aos critérios de ESI-1 ou ESI-2. No ponto C, são necessários recursos: sutura da ferida (procedimento). Apenas 1 recurso foi identificado, levando à classificação ESI-4 (menos urgente).</t>
+        </is>
+      </c>
+      <c r="R78" s="4" t="inlineStr"/>
+      <c r="S78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>35178776</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>Teste rápido de estreptococo (antígeno) ou cultura de garganta</t>
+        </is>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="4" t="inlineStr">
+        <is>
+          <t>Dor de garganta com EVA 5, sem sinais de risco alto, confusão ou dor intensa; vitais normais. Não atende aos pontos A ou B. Necessita de 1 recurso diagnóstico (teste rápido de estreptococo), portanto ponto C indica ESI-4.</t>
+        </is>
+      </c>
+      <c r="R79" s="4" t="inlineStr"/>
+      <c r="S79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>35519971</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>urinalise</t>
+        </is>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N80" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="4" t="inlineStr">
+        <is>
+          <t>Paciente com queixa de disúria leve, sem sinais de gravidade, sem red flags e sinais vitais normais. Não atende aos critérios de ESI-1 ou ESI-2. Necessita de um recurso (urinalise) → ponto C → classificação ESI-4.</t>
+        </is>
+      </c>
+      <c r="R80" s="4" t="inlineStr"/>
+      <c r="S80" s="4" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>36898689</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>ESI-2</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>2</v>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>medicação IV para analgesia
+consulta especializada de queimadura</t>
+        </is>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" t="b">
+        <v>0</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="4" t="inlineStr">
+        <is>
+          <t>Paciente com queimadura apresenta dor intensa (EVA 7), critério do ponto B que determina classificação ESI-2; sinais vitais estáveis e sem necessidade de intervenção imediata, portanto classificação emergente.</t>
+        </is>
+      </c>
+      <c r="R81" s="4" t="inlineStr"/>
+      <c r="S81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>36490072</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>ESI-2</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="4" t="inlineStr"/>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="4" t="inlineStr">
+        <is>
+          <t>Dor dental intensa (EVA 10) → ponto B (dor intensa) → classificação ESI-2</t>
+        </is>
+      </c>
+      <c r="R82" s="4" t="inlineStr"/>
+      <c r="S82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>30281538</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>removal de sutura (procedimento)</t>
+        </is>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="4" t="inlineStr">
+        <is>
+          <t>Paciente sem dor, sem sinais de perigo, requer apenas remoção de sutura, que conta como 1 recurso, atendendo ao ponto C que indica ESI-4</t>
+        </is>
+      </c>
+      <c r="R83" s="4" t="inlineStr"/>
+      <c r="S83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>30449697</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>remoção de grampos (procedimento)</t>
+        </is>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N84" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="4" t="inlineStr">
+        <is>
+          <t>Paciente adulto com sinais vitais estáveis, sem dor, sem red flags e requer apenas um recurso (procedimento de remoção de grampos); ponto C ativado → 1 recurso → classificação ESI-4</t>
+        </is>
+      </c>
+      <c r="R84" s="4" t="inlineStr"/>
+      <c r="S84" s="4" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>30604891</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Não urgente</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="4" t="inlineStr"/>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="4" t="inlineStr">
+        <is>
+          <t>Paciente sem dor, sem sintomas agudos, sinais vitais normais e sem critérios de risco; no ponto C, recursos necessários = 0, levando à classificação ESI-5.</t>
+        </is>
+      </c>
+      <c r="R85" s="4" t="inlineStr"/>
+      <c r="S85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>30754544</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>ESI-2</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>raio-x da mão
+imobilização/splintagem</t>
+        </is>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="4" t="inlineStr">
+        <is>
+          <t>dor no polegar direito com EVA 7/10 caracteriza dor intensa, critério do ponto B que determina classificação ESI-2; sinais vitais normais e sem necessidade de intervenção imediata; portanto classificação emergente</t>
+        </is>
+      </c>
+      <c r="R86" s="4" t="inlineStr"/>
+      <c r="S86" s="4" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>31334118</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>remoção de sutura</t>
+        </is>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N87" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="4" t="inlineStr">
+        <is>
+          <t>Paciente sem dor, sem sinais de risco, vitais estáveis e capaz de caminhar; a única necessidade é a remoção de sutura, que conta como 1 recurso. No ponto C, 1 recurso leva a ESI-4.</t>
+        </is>
+      </c>
+      <c r="R87" s="4" t="inlineStr"/>
+      <c r="S87" s="4" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>31844511</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>ESI-2</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Emergente</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="4" t="inlineStr"/>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" t="b">
+        <v>0</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N88" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="4" t="inlineStr">
+        <is>
+          <t>dor de dente EVA 10 → ponto B (dor intensa) → classificação ESI-2</t>
+        </is>
+      </c>
+      <c r="R88" s="4" t="inlineStr"/>
+      <c r="S88" s="4" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>32284787</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Não urgente</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="4" t="inlineStr"/>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N89" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="4" t="inlineStr">
+        <is>
+          <t>Paciente adulta com queixa de ferida, dor baixa (EVA 1) e sinais vitais dentro dos limites normais; não apresenta red flags nem critérios de alto risco. No ponto C, não são necessários recursos como exames laboratoriais, imagem ou procedimentos invasivos, resultando em 0 recursos → classificação ESI-5 (não urgente).</t>
+        </is>
+      </c>
+      <c r="R89" s="4" t="inlineStr"/>
+      <c r="S89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>33435751</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>medicação IM (vacina antirrábica)</t>
+        </is>
+      </c>
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="L90" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="4" t="inlineStr">
+        <is>
+          <t>Paciente adulta sem dor, sem sintomas graves e sinais vitais dentro dos limites normais. Não há red flags nem critérios de ESI-1 ou ESI-2. Necessita apenas de administração de vacina IM, contabilizado como 1 recurso, levando ao ponto C que indica ESI-4.</t>
+        </is>
+      </c>
+      <c r="R90" s="4" t="inlineStr"/>
+      <c r="S90" s="4" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>34119522</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Menos urgente</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>consulta especializada (enfermagem de ostomia)</t>
+        </is>
+      </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N91" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="4" t="inlineStr">
+        <is>
+          <t>Paciente está estável, sem dor, sem sinais de risco imediato, requer apenas fornecimento de material de ostomia; nenhum recurso crítico, mas há necessidade de consulta especializada para entrega e orientação, totalizando 1 recurso → ponto C → classificação ESI-4</t>
+        </is>
+      </c>
+      <c r="R91" s="4" t="inlineStr"/>
+      <c r="S91" s="4" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>34364911</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Não urgente</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="4" t="inlineStr"/>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92" t="b">
+        <v>0</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N92" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="4" t="inlineStr">
+        <is>
+          <t>Queixa de dor na boca, mas EVA 0, sem sinais de risco, sem sinais vitais na zona de perigo, sem red flags e sem necessidade de recursos (labs, imagem, medicação IV/IM, procedimentos) → ponto C → 0 recursos → classificação ESI-5</t>
+        </is>
+      </c>
+      <c r="R92" s="4" t="inlineStr"/>
+      <c r="S92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>34391933</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Não urgente</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="4" t="inlineStr"/>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="L93" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N93" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="4" t="inlineStr">
+        <is>
+          <t>Queimadura solar sem dor (EVA 0), sem sinais de gravidade, vitais dentro da normalidade e sem necessidade de recursos diagnósticos ou terapêuticos → ponto C → 0 recursos → classificação ESI-5</t>
+        </is>
+      </c>
+      <c r="R93" s="4" t="inlineStr"/>
+      <c r="S93" s="4" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>34467480</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Não urgente</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="4" t="inlineStr"/>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="L94" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N94" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="4" t="inlineStr">
+        <is>
+          <t>dor leve (EVA 2), sem red flags, sinais vitais estáveis e sem necessidade de recursos diagnósticos ou terapêuticos → ponto C ativado → 0 recursos → classificação ESI-5</t>
+        </is>
+      </c>
+      <c r="R94" s="4" t="inlineStr"/>
+      <c r="S94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>35553331</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Não urgente</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="4" t="inlineStr"/>
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="L95" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N95" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="4" t="inlineStr">
+        <is>
+          <t>Sintomas de resfriado leve sem dor, sem sinais de alarme, vitais normais → ponto C, 0 recursos → classificação ESI-5</t>
+        </is>
+      </c>
+      <c r="R95" s="4" t="inlineStr"/>
+      <c r="S95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>35973504</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>ESI-3</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>irrigação ocular
+consulta oftalmológica</t>
+        </is>
+      </c>
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="L96" t="b">
+        <v>0</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="4" t="inlineStr">
+        <is>
+          <t>sintomas de corpo estranho ocular com dor leve (EVA 2) não atendem aos critérios de ESI-1 ou ESI-2; na etapa C foram contados ≥2 recursos (irrigação ocular e consulta oftalmológica), encaminhando ao ponto D; sinais vitais normais, portanto classificação ESI-3</t>
+        </is>
+      </c>
+      <c r="R96" s="4" t="inlineStr"/>
+      <c r="S96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>36219838</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Não urgente</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="4" t="inlineStr"/>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>idoso</t>
+        </is>
+      </c>
+      <c r="L97" t="b">
+        <v>0</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N97" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="4" t="inlineStr">
+        <is>
+          <t>Sem dor, sem sinais de risco, sinais vitais normais e nenhum recurso imediato (exames, medicação IV, procedimentos) necessário → ponto C com 0 recursos → classificação ESI-5</t>
+        </is>
+      </c>
+      <c r="R97" s="4" t="inlineStr"/>
+      <c r="S97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>38695229</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>ESI-3</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>consulta especializada (oftalmologia)</t>
+        </is>
+      </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="L98" t="b">
+        <v>1</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>baixa</t>
+        </is>
+      </c>
+      <c r="N98" s="5" t="inlineStr">
+        <is>
+          <t>NAO</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q98" s="4" t="inlineStr">
+        <is>
+          <t>Sintomas vagos (apenas queixa de avaliação ocular sem dor nem alterações vitais) não atendem aos critérios de ESI-1 ou ESI-2. Com base nas informações disponíveis, estima-se a necessidade de ao menos um recurso (consulta especializada em oftalmologia), o que levaria a ESI-4; porém, por insuficiência de dados, aplica‑se over‑triage para garantir segurança, elevando a classificação para ESI-3.</t>
+        </is>
+      </c>
+      <c r="R98" s="4" t="inlineStr">
+        <is>
+          <t>Qual a data e hora de início da queixa ocular?
+A queixa é contínua ou intermitente?
+Há presença de dor ocular? Se sim, qual a intensidade (EVA 0-10)?
+Existe lacrimejamento, secreção ou descarga ocular?
+Há alterações na visão (visão borrada, perda de visão, fotofobia)?
+Houve trauma ocular recente ou exposição a corpo estranho?
+Uso de lentes de contato ou óculos?
+Histórico de doenças oculares ou cirurgias prévias?
+Uso de medicações atuais ou alergias?
+Alguma condição médica pré‑existente (diabetes, hipertensão, etc.)?</t>
+        </is>
+      </c>
+      <c r="S98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>38885997</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Não urgente</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="4" t="inlineStr"/>
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="L99" t="b">
+        <v>0</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N99" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="4" t="inlineStr">
+        <is>
+          <t>Eritema cutâneo com dor mínima (2/10), sinais vitais estáveis e ausência de red flags ou risco alto → ponto B não satisfeito. Avaliação de recursos necessários revela que nenhum recurso (laboratório, imagem, medicação IV, procedimento) é requerido → ponto C com 0 recursos → classificação ESI-5 (não urgente).</t>
+        </is>
+      </c>
+      <c r="R99" s="4" t="inlineStr"/>
+      <c r="S99" s="4" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>39805389</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Não urgente</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="4" t="inlineStr"/>
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="L100" t="b">
+        <v>0</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N100" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="4" t="inlineStr">
+        <is>
+          <t>Queixa de dor de garganta leve (EVA 2) sem sinais de gravidade, sem red flags, vitais normais e sem necessidade de recursos diagnósticos ou terapêuticos → ponto C com 0 recursos → classificação ESI-5</t>
+        </is>
+      </c>
+      <c r="R100" s="4" t="inlineStr"/>
+      <c r="S100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>39601489</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Não urgente</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="4" t="inlineStr"/>
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="L101" t="b">
+        <v>0</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="N101" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="4" t="inlineStr">
+        <is>
+          <t>Rash sem prurido, dor, edema ou sinais sistêmicos; sinais vitais estáveis; nenhum critério de ESI-1 ou ESI-2 atendido; nenhum recurso imediato necessário (ex.: laboratório, imagem, medicação IV); portanto, ponto C com 0 recursos → classificação ESI-5 (não urgente).</t>
+        </is>
+      </c>
+      <c r="R101" s="4" t="inlineStr"/>
+      <c r="S101" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3204,9 +7937,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ACERTOS POR NÍVEL ESI</t>
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>ACERTOS POR NIVEL ESI</t>
         </is>
       </c>
     </row>
@@ -3238,12 +7971,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="n">
+      <c r="A3" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1 - Ressuscitação</t>
+          <t>1 - Ressuscitacao</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3257,7 +7990,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="12" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -3276,7 +8009,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="13" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -3295,7 +8028,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -3304,321 +8037,337 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr"/>
+      <c r="C8" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>MATRIZ DE CONFUSAO (ESI Ground Truth vs. ESI LLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>GT \ LLM -&gt;</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>ESI-1</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>ESI-2</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>ESI-3</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>ESI-4</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>ESI-5</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>Indeterminado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>1 - Ressuscitacao</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" s="26" t="inlineStr"/>
+      <c r="E11" s="26" t="inlineStr"/>
+      <c r="F11" s="26" t="inlineStr"/>
+      <c r="G11" s="26" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>2 - Emergente</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr"/>
+      <c r="C12" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="26" t="inlineStr"/>
+      <c r="F12" s="26" t="inlineStr"/>
+      <c r="G12" s="26" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>3 - Urgente</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr"/>
+      <c r="C13" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5 - Não urgente</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr"/>
-      <c r="C8" s="15" t="n">
-        <v>66</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>32</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>MATRIZ DE CONFUSÃO (ESI Ground Truth vs. ESI LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>GT \ LLM →</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="D13" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="26" t="inlineStr"/>
+      <c r="G13" s="26" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>4 - Menos urgente</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr"/>
+      <c r="C14" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="26" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>5 - Nao urgente</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr"/>
+      <c r="C15" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="26" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>DISTRIBUICAO DE CLASSIFICACOES LLM POR NIVEL ESI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>ESI</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>ESI-1</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>ESI-2</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>ESI-3</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>ESI-4</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>ESI-5</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>Indeterminado</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>1 - Ressuscitação</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="24" t="n">
+      <c r="H17" s="27" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="D11" s="25" t="inlineStr"/>
-      <c r="E11" s="25" t="inlineStr"/>
-      <c r="F11" s="25" t="inlineStr"/>
-      <c r="G11" s="25" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>2 - Emergente</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr"/>
-      <c r="C12" s="23" t="n">
+      <c r="D18" s="26" t="inlineStr"/>
+      <c r="E18" s="26" t="inlineStr"/>
+      <c r="F18" s="26" t="inlineStr"/>
+      <c r="G18" s="26" t="inlineStr"/>
+      <c r="H18" s="27" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr"/>
+      <c r="C19" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D19" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="25" t="inlineStr"/>
-      <c r="F12" s="25" t="inlineStr"/>
-      <c r="G12" s="25" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>3 - Urgente</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="inlineStr"/>
-      <c r="C13" s="24" t="n">
+      <c r="E19" s="26" t="inlineStr"/>
+      <c r="F19" s="26" t="inlineStr"/>
+      <c r="G19" s="26" t="inlineStr"/>
+      <c r="H19" s="27" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="26" t="inlineStr"/>
+      <c r="C20" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D20" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="E13" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="25" t="inlineStr"/>
-      <c r="G13" s="25" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>4 - Menos urgente</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="inlineStr"/>
-      <c r="C14" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="25" t="inlineStr"/>
-      <c r="G14" s="25" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>5 - Não urgente</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="inlineStr"/>
-      <c r="C15" s="25" t="inlineStr"/>
-      <c r="D15" s="25" t="inlineStr"/>
-      <c r="E15" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="25" t="inlineStr"/>
-      <c r="G15" s="25" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>DISTRIBUIÇÃO DE CLASSIFICAÇÕES LLM POR NÍVEL ESI</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>ESI</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>ESI-1</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>ESI-2</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>ESI-3</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>ESI-4</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>ESI-5</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
-        <is>
-          <t>Indeterminado</t>
-        </is>
-      </c>
-      <c r="H17" s="26" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="D18" s="25" t="inlineStr"/>
-      <c r="E18" s="25" t="inlineStr"/>
-      <c r="F18" s="25" t="inlineStr"/>
-      <c r="G18" s="25" t="inlineStr"/>
-      <c r="H18" s="26" t="n">
+      <c r="E20" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="26" t="inlineStr"/>
+      <c r="G20" s="26" t="inlineStr"/>
+      <c r="H20" s="27" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="25" t="inlineStr"/>
-      <c r="C19" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="D19" s="29" t="n">
+    <row r="21">
+      <c r="A21" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="26" t="inlineStr"/>
+      <c r="C21" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="26" t="inlineStr"/>
+      <c r="H21" s="27" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="26" t="inlineStr"/>
+      <c r="C22" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="E19" s="25" t="inlineStr"/>
-      <c r="F19" s="25" t="inlineStr"/>
-      <c r="G19" s="25" t="inlineStr"/>
-      <c r="H19" s="26" t="n">
+      <c r="F22" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" s="26" t="inlineStr"/>
+      <c r="H22" s="27" t="n">
         <v>20</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="25" t="inlineStr"/>
-      <c r="C20" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="E20" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="25" t="inlineStr"/>
-      <c r="G20" s="25" t="inlineStr"/>
-      <c r="H20" s="26" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" s="25" t="inlineStr"/>
-      <c r="C21" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="25" t="inlineStr"/>
-      <c r="G21" s="25" t="inlineStr"/>
-      <c r="H21" s="26" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="25" t="inlineStr"/>
-      <c r="C22" s="25" t="inlineStr"/>
-      <c r="D22" s="25" t="inlineStr"/>
-      <c r="E22" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="25" t="inlineStr"/>
-      <c r="G22" s="25" t="inlineStr"/>
-      <c r="H22" s="26" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
